--- a/output/laminas_comunales/comunal_o_ocup_a_2022_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,82 +384,622 @@
         </is>
       </c>
       <c r="C2">
-        <v>48.2284887924801</v>
+        <v>66.39566395663959</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C3">
-        <v>47.448416639082</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C4">
-        <v>43.9473684210526</v>
+        <v>63.673308862087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C5">
-        <v>42.0888225378977</v>
+        <v>61.8827160493827</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C6">
-        <v>40.4376272983455</v>
+        <v>58.9713391136802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>58.9381720430108</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>57.9081632653061</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>56.9609584984739</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>56.5144953686996</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>54.1025641025641</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>53.7037037037037</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>48.6237603723943</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>48.2284887924801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>48.1337212940367</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>47.448416639082</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>46.0395439107229</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>45.3476567470526</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>12201</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Cabo de Hornos</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C19">
+        <v>44.9546485260771</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>43.9473684210526</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>42.9052497493021</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>42.7679382379655</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>42.0888225378977</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>41.4191419141914</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>40.6301824212272</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>40.4613466334165</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>40.4376272983455</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>39.5919778699862</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>39.4079685746352</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>38.8155372176377</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>37.8201811125485</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C32">
         <v>35.8693280977312</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>35.6836531780828</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>32.5258799171843</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>31.0975609756098</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>29.5970695970696</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>29.4753086419753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>25.7741347905282</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>23.1981981981982</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>20.4166666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>18.2159810126582</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>15.5653797696184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>11.9577055726992</v>
       </c>
     </row>
   </sheetData>
